--- a/templates/product_import_template.xlsx
+++ b/templates/product_import_template.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>最低價</t>
+          <t>售價</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -650,186 +650,190 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7)「售價」= 給客戶看的售價（對應總表「售價含」）。價格欄（成本/市售價/售價）填 0 視同未提供、不會寫入，請勿把總表「最低特價含」的 0 抄進來。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>【欄位範例】（下一列示範一筆完整資料）</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>分流</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>品牌</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>分類</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>型號</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>主型號</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>商品名稱</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>市售價</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>最低價</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>售價</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>箱入數</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>庫存</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>到貨</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>國際條碼</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>BSMI</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>NCC</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>商品網址</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>大圖網址</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>網路圖</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>ZZ001</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>iCooby</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>滑鼠</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>M-100</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>ZZ001 範例無線滑鼠</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>100</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H13" t="n">
         <v>199</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>159</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>12</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>200</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>現貨</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>4711000000000</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>上架</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.lingdong.com.tw/products/zz001</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>https://example.com/zz001-main.jpg</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://example.com/zz001-1.jpg；https://example.com/zz001-2.jpg</t>
         </is>
